--- a/data/ETCHE/functionsETCHE.xlsx
+++ b/data/ETCHE/functionsETCHE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lochmannm\Documents\GitHub\END2DALY\data\ETCHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07A66CD-6C1A-45F9-AF22-3B157F4F80C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F511B01D-D8FE-421C-91D2-78D599884A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{48A8F245-2396-4F0B-B734-4CFAEB6227B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -199,9 +199,6 @@
     <t>Engelmann ETC HE Report 2024/11, ch 3.3.5</t>
   </si>
   <si>
-    <t>ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - 50))))), 0.1)</t>
-  </si>
-  <si>
     <t>(78.9270 - 3.1162 * c + 0.0342 * c^2)/100</t>
   </si>
   <si>
@@ -251,6 +248,9 @@
   </si>
   <si>
     <t>1-pnorm((72-(-90.70+(c)*(1.80)))/sqrt(1789+272))</t>
+  </si>
+  <si>
+    <t>ifelse (c &gt;= threshold, 1 / (1 + exp(-(log(0.1 / 0.9) + (log(1.38) / 10 * (c - threshold))))), 0.1)</t>
   </si>
 </sst>
 </file>
@@ -310,14 +310,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>74518</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>77555</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>637848</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>87021</xdr:rowOff>
     </xdr:to>
@@ -342,8 +342,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18830925" y="0"/>
-          <a:ext cx="9707330" cy="9132596"/>
+          <a:off x="17578106" y="0"/>
+          <a:ext cx="9707330" cy="9425256"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -448,8 +448,8 @@
       <xdr:rowOff>141720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>27519</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>318872</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>28287</xdr:rowOff>
     </xdr:to>
@@ -811,9 +811,7 @@
     <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="77.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -830,7 +828,7 @@
         <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
         <v>9</v>
@@ -839,22 +837,22 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>31</v>
-      </c>
-      <c r="K1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -874,28 +872,28 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>32</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -915,28 +913,28 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>45</v>
       </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>32</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -956,28 +954,28 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
         <v>2</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>45</v>
       </c>
-      <c r="I4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>32</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -997,28 +995,28 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>45</v>
       </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>32</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -1038,28 +1036,28 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
         <v>3</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>33</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -1079,28 +1077,28 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
         <v>3</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>40</v>
       </c>
-      <c r="I7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>33</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -1120,28 +1118,28 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
         <v>3</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>40</v>
       </c>
-      <c r="I8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>33</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -1161,28 +1159,28 @@
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
         <v>3</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>40</v>
       </c>
-      <c r="I9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>33</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -1202,25 +1200,25 @@
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
         <v>2</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>45</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -1240,25 +1238,25 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
         <v>2</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>45</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -1278,25 +1276,25 @@
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
         <v>2</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>45</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1316,25 +1314,25 @@
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
         <v>2</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>45</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1354,25 +1352,25 @@
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
         <v>2</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>45</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -1392,30 +1390,30 @@
         <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
         <v>2</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>45</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1430,25 +1428,25 @@
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
         <v>66</v>
       </c>
-      <c r="G16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
         <v>53</v>
-      </c>
-      <c r="I16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -1468,25 +1466,25 @@
         <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
         <v>2</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>45</v>
-      </c>
-      <c r="I17" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -1506,25 +1504,25 @@
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
         <v>2</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>45</v>
-      </c>
-      <c r="I18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -1544,25 +1542,25 @@
         <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19" t="s">
         <v>2</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>45</v>
-      </c>
-      <c r="I19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -1582,28 +1580,28 @@
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
         <v>2</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
         <v>50</v>
       </c>
-      <c r="I20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>34</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -1623,28 +1621,28 @@
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
         <v>2</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
         <v>50</v>
       </c>
-      <c r="I21" t="s">
-        <v>51</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>34</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -1664,28 +1662,28 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
         <v>2</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
         <v>50</v>
       </c>
-      <c r="I22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>34</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -1705,25 +1703,25 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
         <v>45</v>
-      </c>
-      <c r="I23" t="s">
-        <v>50</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -1743,25 +1741,25 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
         <v>45</v>
-      </c>
-      <c r="I24" t="s">
-        <v>50</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -1781,25 +1779,25 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
         <v>45</v>
-      </c>
-      <c r="I25" t="s">
-        <v>50</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -1819,25 +1817,25 @@
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
         <v>2</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
         <v>45</v>
-      </c>
-      <c r="I26" t="s">
-        <v>52</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -1857,25 +1855,25 @@
         <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
         <v>2</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
         <v>45</v>
-      </c>
-      <c r="I27" t="s">
-        <v>52</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -1895,25 +1893,25 @@
         <v>6</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
         <v>45</v>
-      </c>
-      <c r="I28" t="s">
-        <v>52</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
